--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-order-information.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-order-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-order-information.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-order-information.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="120">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Order Information</t>
+    <t>Logical model - FR LM Order Information</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -373,6 +373,16 @@
   </si>
   <si>
     <t>fr-lm-section.entry</t>
+  </si>
+  <si>
+    <t>fr-lm-order-information.entry.orderInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-service-request
+</t>
+  </si>
+  <si>
+    <t>Entrée Demande d'examen d'imagerie</t>
   </si>
 </sst>
 </file>
@@ -674,7 +684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.66796875" customWidth="true" bestFit="true"/>
@@ -708,7 +718,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="37.58203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1840,7 +1850,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1921,6 +1931,106 @@
         <v>73</v>
       </c>
       <c r="AJ12" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>73</v>
       </c>
     </row>
